--- a/kanban_system/output/library_linked/摩尔多瓦法规清单.xlsx
+++ b/kanban_system/output/library_linked/摩尔多瓦法规清单.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摩尔多瓦" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="摩尔多瓦" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'摩尔多瓦'!$A$1:$Y$11</definedName>
@@ -11145,6 +11145,11 @@
         </is>
       </c>
       <c r="Y108" s="16" t="n"/>
+      <c r="Z108" s="22" t="inlineStr">
+        <is>
+          <t>INS-2026-015 驾驶员前方视野校核指南 | GB 11562-2025</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="14" customFormat="1" customHeight="1" s="18">
       <c r="A109" s="19" t="n">
@@ -15825,7 +15830,7 @@
       <c r="Y156" s="16" t="n"/>
       <c r="Z156" s="22" t="inlineStr">
         <is>
-          <t>INS-2026-008 国内首个车载HUD法规正式发布：区域1和区域2要求详解</t>
+          <t>INS-2026-008 国内首个车载HUD法规正式发布：区域1和区域2要求详解 ; INS-2026-015 驾驶员前方视野校核指南 | GB 11562-2025</t>
         </is>
       </c>
     </row>

--- a/kanban_system/output/library_linked/摩尔多瓦法规清单.xlsx
+++ b/kanban_system/output/library_linked/摩尔多瓦法规清单.xlsx
@@ -6893,6 +6893,11 @@
         </is>
       </c>
       <c r="Y64" s="16" t="n"/>
+      <c r="Z64" s="22" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="14" customFormat="1" customHeight="1" s="18">
       <c r="A65" s="19" t="n">
@@ -8543,6 +8548,11 @@
         </is>
       </c>
       <c r="Y81" s="16" t="n"/>
+      <c r="Z81" s="22" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="14" customFormat="1" customHeight="1" s="18">
       <c r="A82" s="19" t="n">
@@ -8642,7 +8652,7 @@
       <c r="Y82" s="16" t="n"/>
       <c r="Z82" s="22" t="inlineStr">
         <is>
-          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别</t>
+          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别 ; INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
         </is>
       </c>
     </row>
